--- a/outputs/daily/hr_rankings_2026-08-15_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-15_remaining.xlsx
@@ -1368,7 +1368,7 @@
         <v>46.2</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5572,7 +5572,7 @@
         <v>46.9</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S19" t="n">
         <v>96.59999999999999</v>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -10350,34 +10350,30 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10568,7 +10564,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -13928,7 +13924,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14208,7 +14204,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14747,27 +14743,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>691723</t>
+          <t>677594</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Julio Rodríguez</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-15T22:10:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -14782,21 +14778,21 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14810,26 +14806,26 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>47.3</v>
+        <v>46.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>40.9</v>
+        <v>46.9</v>
       </c>
       <c r="R52" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S52" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>24.9</v>
+        <v>54.7</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -14886,22 +14882,22 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 10.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -14911,97 +14907,97 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>102.6095</t>
+          <t>102.6557</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.3973</t>
+          <t>0.4692</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.195</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.2974</t>
+          <t>0.3482</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>76.61</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>54.04</t>
+          <t>66.85</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>38.49</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>26.33</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.2032</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>0.3816</t>
+          <t>0.4563</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
@@ -15011,12 +15007,12 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr"/>
@@ -15027,32 +15023,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>677594</t>
+          <t>691723</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Julio Rodríguez</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T22:10:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -15062,17 +15058,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -15090,14 +15086,14 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>46.2</v>
+        <v>47.3</v>
       </c>
       <c r="Q53" t="n">
-        <v>46.9</v>
+        <v>40.9</v>
       </c>
       <c r="R53" t="n">
         <v>41.1</v>
@@ -15106,10 +15102,10 @@
         <v>94.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U53" t="n">
-        <v>54.7</v>
+        <v>24.9</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -15166,22 +15162,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 3.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 10.6 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15191,97 +15187,97 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>102.6557</t>
+          <t>102.6095</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.4692</t>
+          <t>0.3973</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3482</t>
+          <t>0.2974</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>76.61</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>66.85</t>
+          <t>54.04</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>38.49</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.2032</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.4563</t>
+          <t>0.3816</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
@@ -15296,7 +15292,7 @@
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15682,34 +15678,30 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -17044,7 +17036,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -17068,7 +17060,7 @@
         <v>46.9</v>
       </c>
       <c r="R60" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S60" t="n">
         <v>100</v>
@@ -17259,7 +17251,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI60" t="inlineStr">
@@ -17628,7 +17620,7 @@
         <v>46.5</v>
       </c>
       <c r="R62" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S62" t="n">
         <v>64.3</v>
@@ -17819,7 +17811,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI62" t="inlineStr">
@@ -19584,7 +19576,7 @@
         <v>46.2</v>
       </c>
       <c r="R69" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S69" t="n">
         <v>94.90000000000001</v>
@@ -19775,7 +19767,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
@@ -20162,34 +20154,30 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20446,34 +20434,30 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -21832,7 +21816,7 @@
         <v>46.2</v>
       </c>
       <c r="R77" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S77" t="n">
         <v>64.3</v>
@@ -22023,7 +22007,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
@@ -23184,7 +23168,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -23744,7 +23728,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -24048,7 +24032,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -24072,7 +24056,7 @@
         <v>46.9</v>
       </c>
       <c r="R85" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S85" t="n">
         <v>86.40000000000001</v>
@@ -24263,7 +24247,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI85" t="inlineStr">
@@ -24352,7 +24336,7 @@
         <v>46.2</v>
       </c>
       <c r="R86" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S86" t="n">
         <v>76.2</v>
@@ -24543,7 +24527,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI86" t="inlineStr">
@@ -24559,27 +24543,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-16T01:40:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -24589,22 +24573,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>676106</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -24622,54 +24606,58 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>36</v>
+        <v>42.7</v>
       </c>
       <c r="Q87" t="n">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="R87" t="n">
-        <v>56.4</v>
+        <v>41.6</v>
       </c>
       <c r="S87" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T87" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U87" t="n">
-        <v>5.7</v>
+        <v>91.5</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y87" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24689,27 +24677,27 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 17.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
@@ -24719,112 +24707,112 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>43.88</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>101.0992</t>
+          <t>101.7237</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.4194</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.1444</t>
+          <t>0.176</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.3215</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>74.01</t>
+          <t>76.74</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>68.32</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>42.82</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>25.07</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.1552</t>
+          <t>0.1584</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.4316</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.1523</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>27.79</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -24835,27 +24823,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-16T01:40:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -24865,26 +24853,26 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>676106</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -24898,26 +24886,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Strong Barrel, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>42.7</v>
+        <v>36</v>
       </c>
       <c r="Q88" t="n">
-        <v>46.2</v>
+        <v>46.8</v>
       </c>
       <c r="R88" t="n">
-        <v>41.1</v>
+        <v>56.4</v>
       </c>
       <c r="S88" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T88" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U88" t="n">
-        <v>91.5</v>
+        <v>5.7</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24931,7 +24919,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -24969,27 +24957,27 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 3/19, 0 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 17.9 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -24999,112 +24987,112 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>10.33</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>43.88</t>
+          <t>41.01</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>101.7237</t>
+          <t>101.0992</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.4194</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>74.01</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>68.32</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>42.82</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>25.07</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1584</t>
+          <t>0.1552</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.4316</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1523</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>27.79</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -25762,34 +25750,30 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30536,28 +30520,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr"/>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y108" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -30748,7 +30736,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -31563,27 +31551,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>665161</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Jeremy Peña</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -31593,17 +31581,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Jared Jones</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>683003</t>
+          <t>676106</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -31630,22 +31618,22 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>22.5</v>
+        <v>29.7</v>
       </c>
       <c r="Q112" t="n">
-        <v>40</v>
+        <v>46.2</v>
       </c>
       <c r="R112" t="n">
-        <v>45.8</v>
+        <v>41.6</v>
       </c>
       <c r="S112" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T112" t="n">
         <v>50</v>
       </c>
       <c r="U112" t="n">
-        <v>45.3</v>
+        <v>0</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31659,7 +31647,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -31680,7 +31668,7 @@
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr"/>
@@ -31697,27 +31685,27 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Last 7 games: 9/30, 1 HR</t>
+          <t>Last 7 games: 3/31, 0 HR</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -31727,112 +31715,112 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>34.22</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.48</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>97.8061</t>
+          <t>99.9946</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.3796</t>
+          <t>0.425</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1445</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.2924</t>
+          <t>0.3354</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>72.23</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>35.64</t>
+          <t>45.85</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>23.03</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.1748</t>
+          <t>0.1786</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.4316</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -31843,27 +31831,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>665161</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jeremy Peña</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -31873,17 +31861,17 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>Jared Jones</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>676106</t>
+          <t>683003</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -31892,7 +31880,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -31910,22 +31898,22 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>29.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q113" t="n">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="R113" t="n">
-        <v>41.1</v>
+        <v>45.8</v>
       </c>
       <c r="S113" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T113" t="n">
         <v>50</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>45.3</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31939,7 +31927,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -31960,7 +31948,7 @@
       <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr"/>
@@ -31977,27 +31965,27 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/31, 0 HR</t>
+          <t>Last 7 games: 9/30, 1 HR</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -32007,112 +31995,112 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>34.22</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>88.48</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>99.9946</t>
+          <t>97.8061</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.425</t>
+          <t>0.3796</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.1445</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.3354</t>
+          <t>0.2924</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>72.23</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>35.64</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.1786</t>
+          <t>0.1748</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.4316</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI113" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ113" t="inlineStr"/>
@@ -34156,7 +34144,7 @@
         <v>46.9</v>
       </c>
       <c r="R121" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S121" t="n">
         <v>76.2</v>
@@ -34347,7 +34335,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI121" t="inlineStr">
@@ -35252,7 +35240,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -35276,7 +35264,7 @@
         <v>46.9</v>
       </c>
       <c r="R125" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S125" t="n">
         <v>93.2</v>
@@ -35467,7 +35455,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI125" t="inlineStr">
@@ -36043,27 +36031,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>681047</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Christian Franklin</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-15T22:10:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -36073,26 +36061,26 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>676106</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -36106,26 +36094,26 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>32.1</v>
+        <v>17.9</v>
       </c>
       <c r="Q128" t="n">
-        <v>40.9</v>
+        <v>46.2</v>
       </c>
       <c r="R128" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S128" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T128" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U128" t="n">
-        <v>7</v>
+        <v>33.7</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -36139,7 +36127,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -36160,7 +36148,7 @@
       <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr"/>
@@ -36177,12 +36165,12 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ128" t="inlineStr">
@@ -36192,12 +36180,12 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 0 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL128" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.1% barrel, 10.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -36207,97 +36195,97 @@
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>5.53</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>30.03</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>86.42</t>
         </is>
       </c>
       <c r="AQ128" t="inlineStr">
         <is>
-          <t>97.1896</t>
+          <t>96.906</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.3737</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>0.1306</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>67.81</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>52.07</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.1732</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="BD128" t="inlineStr">
         <is>
-          <t>0.3816</t>
+          <t>0.4316</t>
         </is>
       </c>
       <c r="BE128" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BF128" t="inlineStr">
         <is>
-          <t>29.52</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="BG128" t="inlineStr">
@@ -36307,12 +36295,12 @@
       </c>
       <c r="BH128" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI128" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ128" t="inlineStr"/>
@@ -36323,52 +36311,52 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>681047</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Christian Franklin</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T22:10:00Z</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>676106</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -36386,26 +36374,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>17.9</v>
+        <v>32.1</v>
       </c>
       <c r="Q129" t="n">
-        <v>46.2</v>
+        <v>40.9</v>
       </c>
       <c r="R129" t="n">
         <v>41.1</v>
       </c>
       <c r="S129" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T129" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U129" t="n">
-        <v>33.7</v>
+        <v>7</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -36419,7 +36407,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -36440,7 +36428,7 @@
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr"/>
@@ -36457,12 +36445,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -36472,12 +36460,12 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.1% barrel, 10.6 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -36487,97 +36475,97 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>5.53</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>30.03</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>86.42</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>96.906</t>
+          <t>97.1896</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.3737</t>
+          <t>0.255</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1306</t>
+          <t>0.104</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>67.81</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1732</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>38.36</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.4316</t>
+          <t>0.3816</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>29.52</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
@@ -36592,7 +36580,7 @@
       </c>
       <c r="BI129" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ129" t="inlineStr"/>
@@ -38090,34 +38078,30 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -40552,7 +40536,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -40807,27 +40791,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>514888</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Jose Altuve</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-15T23:15:00Z</t>
+          <t>2026-08-15T23:10:00Z</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -40837,22 +40821,22 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>Emerson Hancock</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>676106</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L145" t="n">
@@ -40870,26 +40854,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="Q145" t="n">
-        <v>42.1</v>
+        <v>46.2</v>
       </c>
       <c r="R145" t="n">
-        <v>73.90000000000001</v>
+        <v>41.6</v>
       </c>
       <c r="S145" t="n">
-        <v>44.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T145" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U145" t="n">
-        <v>6</v>
+        <v>37.8</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -40903,7 +40887,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -40941,27 +40925,27 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 16.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -40971,112 +40955,112 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.24</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>100.5941</t>
+          <t>97.0039</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>0.3497</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.0873</t>
+          <t>0.1204</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.2041</t>
+          <t>0.2846</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>70.85</t>
+          <t>69.07</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>56.61</t>
+          <t>46.27</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.0882</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>35.76</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>88.13</t>
+          <t>89.35</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4405</t>
+          <t>0.4316</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1762</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>28.52</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH145" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr"/>
@@ -41087,22 +41071,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>669221</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>Sean Murphy</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -41122,17 +41106,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -41154,22 +41138,22 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>31</v>
+        <v>17.8</v>
       </c>
       <c r="Q146" t="n">
-        <v>18.2</v>
+        <v>42.1</v>
       </c>
       <c r="R146" t="n">
-        <v>70.09999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="S146" t="n">
         <v>44.8</v>
       </c>
       <c r="T146" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U146" t="n">
-        <v>40.3</v>
+        <v>6</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -41226,22 +41210,22 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.8% barrel, 11.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -41251,112 +41235,112 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>40.93</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>98.9776</t>
+          <t>100.5941</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3601</t>
+          <t>0.261</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1325</t>
+          <t>0.0873</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.3023</t>
+          <t>0.2041</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>70.78</t>
+          <t>70.85</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>56.61</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1004</t>
+          <t>0.0882</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>8.34</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>35.76</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>88.13</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>0.4405</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1762</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH146" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>92</t>
         </is>
       </c>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -41367,27 +41351,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>514888</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Jose Altuve</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-15T23:10:00Z</t>
+          <t>2026-08-15T23:15:00Z</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -41397,17 +41381,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Emerson Hancock</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>676106</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -41416,7 +41400,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -41430,26 +41414,26 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>14.4</v>
+        <v>31</v>
       </c>
       <c r="Q147" t="n">
-        <v>46.2</v>
+        <v>18.2</v>
       </c>
       <c r="R147" t="n">
-        <v>41.1</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="S147" t="n">
-        <v>86.40000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T147" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U147" t="n">
-        <v>37.8</v>
+        <v>40.3</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -41463,7 +41447,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -41501,12 +41485,12 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -41516,12 +41500,12 @@
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/15, 1 HR</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.8% barrel, 11.5 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -41531,112 +41515,112 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>85.24</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>97.0039</t>
+          <t>98.9776</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.3497</t>
+          <t>0.3601</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.1325</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.2846</t>
+          <t>0.3023</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>70.78</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>46.27</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1004</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>89.35</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.4316</t>
+          <t>0.274</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.1717</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>25.71</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH147" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -41672,7 +41656,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -43632,7 +43616,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -43912,7 +43896,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -44524,7 +44508,7 @@
         <v>46.5</v>
       </c>
       <c r="R158" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S158" t="n">
         <v>44.8</v>
@@ -44715,7 +44699,7 @@
       </c>
       <c r="BH158" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI158" t="inlineStr">
@@ -44822,34 +44806,30 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB159" t="inlineStr"/>
       <c r="AC159" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -45040,7 +45020,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -45320,7 +45300,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -45880,7 +45860,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -49276,7 +49256,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -49300,7 +49280,7 @@
         <v>46.9</v>
       </c>
       <c r="R175" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S175" t="n">
         <v>52.4</v>
@@ -49491,7 +49471,7 @@
       </c>
       <c r="BH175" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI175" t="inlineStr">
@@ -49812,7 +49792,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -50116,7 +50096,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="M178" t="inlineStr">
         <is>
@@ -50140,7 +50120,7 @@
         <v>46.2</v>
       </c>
       <c r="R178" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S178" t="n">
         <v>44.8</v>
@@ -50331,7 +50311,7 @@
       </c>
       <c r="BH178" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI178" t="inlineStr">
@@ -52150,7 +52130,7 @@
         <v>46.2</v>
       </c>
       <c r="R4" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -52341,7 +52321,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -52658,7 +52638,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -56354,7 +56334,7 @@
         <v>46.9</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>41.6</v>
       </c>
       <c r="S19" t="n">
         <v>96.59999999999999</v>
@@ -56545,7 +56525,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-15_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-15_remaining.xlsx
@@ -2222,34 +2222,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3346,34 +3342,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8394,34 +8386,30 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23510,34 +23498,30 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24358,34 +24342,30 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24920,28 +24900,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="Y88" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26318,34 +26302,30 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36396,28 +36376,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W129" t="inlineStr"/>
-      <c r="X129" t="inlineStr"/>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y129" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -40870,34 +40854,30 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB145" t="inlineStr"/>
       <c r="AC145" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -47928,34 +47908,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -49052,34 +49028,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
